--- a/data/trans_camb/IP1003-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 0,5</t>
+          <t>-4,67; 0,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 1,65</t>
+          <t>-3,2; 2,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,5</t>
+          <t>-3,74; 0,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,17</t>
+          <t>-4,94; 1,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,48</t>
+          <t>-5,37; 0,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 0,84</t>
+          <t>-5,31; 0,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,28</t>
+          <t>-3,7; 0,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,6</t>
+          <t>-3,55; 0,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,15</t>
+          <t>-3,76; 0,36</t>
         </is>
       </c>
     </row>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,27; 48,87</t>
+          <t>-91,52; 56,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-89,25; 81,21</t>
+          <t>-89,5; 86,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 115,47</t>
+          <t>-100,0; 133,87</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,74</t>
+          <t>-5,89; 1,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 0,06</t>
+          <t>-6,49; 0,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 0,22</t>
+          <t>-6,17; 1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 3,45</t>
+          <t>-3,35; 3,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 1,89</t>
+          <t>-4,32; 2,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 3,29</t>
+          <t>-4,18; 3,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 1,23</t>
+          <t>-3,53; 1,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 0,28</t>
+          <t>-4,38; 0,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 0,98</t>
+          <t>-4,18; 1,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-67,76; 19,61</t>
+          <t>-69,18; 29,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,79; 10,37</t>
+          <t>-77,76; 9,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,49; 11,89</t>
+          <t>-78,64; 25,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-43,39; 79,22</t>
+          <t>-45,12; 92,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 49,05</t>
+          <t>-57,69; 57,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,89; 82,18</t>
+          <t>-57,63; 90,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,27; 26,55</t>
+          <t>-47,67; 25,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,26; 8,94</t>
+          <t>-57,61; 10,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-60,49; 20,21</t>
+          <t>-58,68; 26,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 3,11</t>
+          <t>-7,82; 2,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 3,49</t>
+          <t>-6,78; 3,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 2,05</t>
+          <t>-7,76; 2,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 5,77</t>
+          <t>-5,48; 6,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 2,6</t>
+          <t>-6,58; 2,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 5,79</t>
+          <t>-5,99; 5,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,81</t>
+          <t>-4,6; 2,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,84</t>
+          <t>-5,46; 1,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,27</t>
+          <t>-5,0; 2,49</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 63,25</t>
+          <t>-64,66; 51,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-57,97; 61,69</t>
+          <t>-58,49; 55,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-67,27; 41,57</t>
+          <t>-65,67; 45,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,68; 96,21</t>
+          <t>-45,5; 105,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-61,05; 42,53</t>
+          <t>-60,06; 49,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,91; 103,24</t>
+          <t>-51,67; 87,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-45,03; 40,79</t>
+          <t>-42,66; 43,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 31,58</t>
+          <t>-49,13; 26,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,58; 36,34</t>
+          <t>-47,23; 37,26</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 6,39</t>
+          <t>-1,98; 6,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 3,53</t>
+          <t>-4,18; 3,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,14</t>
+          <t>-2,28; 5,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 2,98</t>
+          <t>-6,25; 2,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 3,14</t>
+          <t>-6,52; 2,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 7,34</t>
+          <t>-2,77; 6,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 3,14</t>
+          <t>-3,35; 3,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 2,28</t>
+          <t>-4,42; 1,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,93</t>
+          <t>-1,47; 4,81</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-34,25; 164,55</t>
+          <t>-28,93; 157,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-53,76; 88,9</t>
+          <t>-57,33; 86,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 127,86</t>
+          <t>-32,55; 140,13</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 44,2</t>
+          <t>-56,67; 47,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-58,98; 49,23</t>
+          <t>-60,21; 41,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 110,28</t>
+          <t>-24,32; 100,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 51,84</t>
+          <t>-38,5; 50,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 33,62</t>
+          <t>-48,62; 28,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 79,44</t>
+          <t>-15,12; 79,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 0,77</t>
+          <t>-3,34; 0,53</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,41</t>
+          <t>-3,31; 0,79</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 1,78</t>
+          <t>-2,49; 1,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,33</t>
+          <t>-3,09; 1,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,33</t>
+          <t>-3,72; 0,32</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,77</t>
+          <t>-0,99; 3,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,47</t>
+          <t>-2,52; 0,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,02; -0,09</t>
+          <t>-3,1; -0,21</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 1,97</t>
+          <t>-1,23; 2,12</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 16,19</t>
+          <t>-47,17; 11,26</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 9,86</t>
+          <t>-47,9; 16,58</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 35,91</t>
+          <t>-36,19; 32,58</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 22,87</t>
+          <t>-38,44; 19,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 4,8</t>
+          <t>-46,52; 5,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 65,54</t>
+          <t>-13,36; 66,37</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-33,41; 8,63</t>
+          <t>-34,92; 7,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,67; -1,35</t>
+          <t>-43,33; -3,28</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,78; 36,45</t>
+          <t>-16,5; 36,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,41</t>
+          <t>-4,09; 0,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 2,03</t>
+          <t>-3,4; 1,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,55</t>
+          <t>-4,05; 0,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,11</t>
+          <t>-5,66; 0,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 0,53</t>
+          <t>-5,55; 0,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,88</t>
+          <t>-5,04; 1,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,33</t>
+          <t>-3,39; 0,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,57</t>
+          <t>-3,36; 0,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,36</t>
+          <t>-3,69; 0,25</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 107,03</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 113,16</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,52; 56,11</t>
+          <t>-90,21; 57,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-89,5; 86,09</t>
+          <t>-88,93; 71,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 133,87</t>
+          <t>-100,0; 86,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 1,11</t>
+          <t>-5,53; 1,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 0,23</t>
+          <t>-6,29; 0,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 1,04</t>
+          <t>-6,41; 0,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,67</t>
+          <t>-3,44; 3,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,23</t>
+          <t>-4,15; 2,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 3,64</t>
+          <t>-4,06; 3,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 1,29</t>
+          <t>-3,5; 1,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,38</t>
+          <t>-4,35; 0,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 1,16</t>
+          <t>-4,19; 1,0</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,18; 29,43</t>
+          <t>-68,68; 23,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,76; 9,92</t>
+          <t>-75,45; 19,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,64; 25,57</t>
+          <t>-78,23; 17,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 92,34</t>
+          <t>-44,39; 85,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,69; 57,21</t>
+          <t>-56,8; 53,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 90,0</t>
+          <t>-57,81; 90,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,67; 25,98</t>
+          <t>-45,4; 29,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-57,61; 10,73</t>
+          <t>-59,92; 10,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 26,13</t>
+          <t>-56,71; 21,04</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 2,93</t>
+          <t>-7,39; 2,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 3,02</t>
+          <t>-6,69; 3,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,76; 2,52</t>
+          <t>-8,31; 2,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 6,08</t>
+          <t>-4,78; 5,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 2,68</t>
+          <t>-7,14; 2,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 5,21</t>
+          <t>-5,19; 5,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 2,99</t>
+          <t>-4,83; 2,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 1,61</t>
+          <t>-5,45; 1,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 2,49</t>
+          <t>-5,24; 2,75</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-64,66; 51,06</t>
+          <t>-65,9; 46,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-58,49; 55,67</t>
+          <t>-55,54; 77,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,67; 45,44</t>
+          <t>-68,53; 40,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,5; 105,11</t>
+          <t>-42,87; 89,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,06; 49,09</t>
+          <t>-62,83; 46,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 87,6</t>
+          <t>-48,11; 86,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 43,54</t>
+          <t>-43,72; 40,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,13; 26,44</t>
+          <t>-49,09; 30,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-47,23; 37,26</t>
+          <t>-50,24; 42,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 6,11</t>
+          <t>-2,28; 6,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 3,49</t>
+          <t>-4,03; 3,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 5,62</t>
+          <t>-2,45; 5,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 2,95</t>
+          <t>-6,34; 2,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 2,89</t>
+          <t>-6,55; 2,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,99</t>
+          <t>-2,58; 6,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,12</t>
+          <t>-3,58; 2,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 1,55</t>
+          <t>-4,31; 2,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,81</t>
+          <t>-1,34; 4,84</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,93; 157,63</t>
+          <t>-32,06; 149,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,33; 86,71</t>
+          <t>-53,25; 92,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 140,13</t>
+          <t>-31,69; 135,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,67; 47,78</t>
+          <t>-56,29; 38,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-60,21; 41,89</t>
+          <t>-57,91; 41,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 100,67</t>
+          <t>-23,83; 94,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,5; 50,99</t>
+          <t>-38,39; 43,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-48,62; 28,01</t>
+          <t>-47,67; 32,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,12; 79,52</t>
+          <t>-15,67; 78,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,53</t>
+          <t>-3,36; 0,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,79</t>
+          <t>-3,49; 0,59</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 1,63</t>
+          <t>-2,58; 1,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,13</t>
+          <t>-3,0; 1,21</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,32</t>
+          <t>-3,9; 0,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,85</t>
+          <t>-1,11; 3,97</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,44</t>
+          <t>-2,45; 0,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,1; -0,21</t>
+          <t>-3,03; -0,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,12</t>
+          <t>-1,24; 2,08</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 11,26</t>
+          <t>-46,6; 16,39</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,9; 16,58</t>
+          <t>-49,28; 11,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 32,58</t>
+          <t>-36,71; 34,74</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 19,19</t>
+          <t>-37,68; 21,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,52; 5,85</t>
+          <t>-47,77; 5,43</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 66,37</t>
+          <t>-13,97; 66,04</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,92; 7,84</t>
+          <t>-35,55; 7,16</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-43,33; -3,28</t>
+          <t>-42,14; -1,23</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 36,3</t>
+          <t>-18,33; 36,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1003-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP1003-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,91</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,98</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-0,38</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-1,66</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,5</t>
+          <t>-4,88; 1,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 1,82</t>
+          <t>-5,46; 0,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,66</t>
+          <t>-5,52; 0,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 0,77</t>
+          <t>-3,95; 0,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 0,51</t>
+          <t>-3,48; 1,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,4</t>
+          <t>-4,47; 0,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 0,37</t>
+          <t>-3,39; 0,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,58</t>
+          <t>-3,35; 0,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 0,25</t>
+          <t>-3,88; 0,07</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-51,8%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-64,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-66,88%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-71,1%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-21,76%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-68,26%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-51,8%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-64,52%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-67,15%</t>
+          <t>-71,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-67,78%</t>
+          <t>-69,35%</t>
         </is>
       </c>
     </row>
@@ -798,12 +798,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 107,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 113,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-90,21; 57,96</t>
+          <t>-91,27; 48,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,93; 71,29</t>
+          <t>-89,25; 81,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 86,39</t>
+          <t>-100,0; 108,56</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,06</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,17</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,64</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-2,37</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-3,16</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-3,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,06</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,17</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-2,63</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-1,85</t>
+          <t>-2,13</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 1,04</t>
+          <t>-3,39; 3,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,06</t>
+          <t>-4,56; 1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 0,42</t>
+          <t>-4,69; 1,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 3,49</t>
+          <t>-5,6; 0,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,26</t>
+          <t>-6,44; 0,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 3,36</t>
+          <t>-6,4; 0,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 1,43</t>
+          <t>-3,63; 1,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 0,38</t>
+          <t>-4,39; 0,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 1,0</t>
+          <t>-4,61; 0,39</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-19,85%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-27,89%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-36,45%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-48,69%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-46,84%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-19,85%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-13,06%</t>
+          <t>-40,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-29,84%</t>
+          <t>-34,39%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-68,68; 23,43</t>
+          <t>-43,39; 79,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,45; 19,72</t>
+          <t>-58,42; 49,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,23; 17,8</t>
+          <t>-63,7; 51,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-44,39; 85,19</t>
+          <t>-67,76; 19,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 53,82</t>
+          <t>-77,79; 10,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,81; 90,11</t>
+          <t>-79,32; 23,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,4; 29,4</t>
+          <t>-49,27; 26,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-59,92; 10,57</t>
+          <t>-59,26; 8,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 21,04</t>
+          <t>-63,44; 8,06</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,48</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,55</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-1,35</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,57</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-1,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 2,72</t>
+          <t>-5,17; 5,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 3,69</t>
+          <t>-6,97; 2,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 2,02</t>
+          <t>-5,93; 5,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,71</t>
+          <t>-7,74; 3,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 2,72</t>
+          <t>-6,67; 3,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 5,55</t>
+          <t>-7,63; 2,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 2,68</t>
+          <t>-4,91; 2,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 1,9</t>
+          <t>-5,58; 1,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,75</t>
+          <t>-4,82; 2,05</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,44%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-24,68%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-6,21%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-25,98%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-15,66%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-29,87%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,44%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-24,68%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-2,61%</t>
+          <t>-26,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-14,67%</t>
+          <t>-15,39%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-65,9; 46,24</t>
+          <t>-42,68; 96,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,54; 77,05</t>
+          <t>-61,05; 42,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,53; 40,22</t>
+          <t>-51,21; 94,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,87; 89,17</t>
+          <t>-64,06; 63,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 46,33</t>
+          <t>-57,97; 61,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-48,11; 86,42</t>
+          <t>-65,16; 45,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,72; 40,36</t>
+          <t>-45,03; 40,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,09; 30,1</t>
+          <t>-51,14; 31,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,24; 42,75</t>
+          <t>-46,93; 34,8</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,92</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,96</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,71</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,69</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,32</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,53</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,96</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,39</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>2,62</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 6,24</t>
+          <t>-6,23; 2,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 3,49</t>
+          <t>-6,62; 3,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 5,48</t>
+          <t>-1,74; 8,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 2,61</t>
+          <t>-2,44; 6,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 2,81</t>
+          <t>-4,11; 3,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 6,88</t>
+          <t>-1,77; 6,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,75</t>
+          <t>-3,29; 3,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,01</t>
+          <t>-3,93; 2,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 4,84</t>
+          <t>-0,64; 6,14</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-20,82%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-21,35%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>29,45%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>28,81%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-5,38%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>26,12%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-20,82%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-21,35%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,06; 149,01</t>
+          <t>-56,71; 44,2</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-53,25; 92,5</t>
+          <t>-58,98; 49,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 135,66</t>
+          <t>-15,73; 122,26</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,29; 38,51</t>
+          <t>-34,25; 164,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-57,91; 41,65</t>
+          <t>-53,76; 88,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 94,67</t>
+          <t>-26,03; 149,14</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 43,02</t>
+          <t>-36,27; 51,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,67; 32,93</t>
+          <t>-45,42; 33,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 78,13</t>
+          <t>-7,88; 95,15</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,81</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,73</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,45</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-1,27</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-1,41</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,73</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,75</t>
+          <t>-2,86; 1,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,59</t>
+          <t>-3,59; 0,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,82</t>
+          <t>-0,9; 3,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,21</t>
+          <t>-3,24; 0,77</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 0,26</t>
+          <t>-3,52; 0,41</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,97</t>
+          <t>-2,02; 2,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,45</t>
+          <t>-2,37; 0,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; -0,11</t>
+          <t>-3,02; -0,09</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 2,08</t>
+          <t>-0,81; 2,44</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-11,71%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-25,05%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20,96%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-21,26%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-23,55%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-7,61%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-11,71%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-25,05%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>12,81%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-46,6; 16,39</t>
+          <t>-36,97; 22,87</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-49,28; 11,42</t>
+          <t>-46,7; 4,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 34,74</t>
+          <t>-12,58; 68,31</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,68; 21,22</t>
+          <t>-46,57; 16,19</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 5,43</t>
+          <t>-49,62; 9,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 66,04</t>
+          <t>-29,43; 48,49</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 7,16</t>
+          <t>-33,41; 8,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,14; -1,23</t>
+          <t>-41,67; -1,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-18,33; 36,45</t>
+          <t>-11,57; 41,23</t>
         </is>
       </c>
     </row>
